--- a/report-backend/src/main/resources/informationTemplate.xlsx
+++ b/report-backend/src/main/resources/informationTemplate.xlsx
@@ -1,310 +1,193 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25920" windowHeight="13715"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="13715" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>批量上传文件并生成数据表模板</t>
-  </si>
-  <si>
-    <t>序号
-(必填)</t>
-  </si>
-  <si>
-    <t>文件名
-(必填,仅支持字母开头，且只能包含字母,下划线和数字;带后缀,支持txt,csv,xls,xlsx)</t>
-  </si>
-  <si>
-    <t>目标表类型
-(必填,hive/mpp)</t>
-  </si>
-  <si>
-    <t>目标库名
-(hive时必填可写库库名,mpp时必填mppSchema)</t>
-  </si>
-  <si>
-    <t>目标表名
-(必填,bi_前缀不用填写,会自动拼接上)</t>
-  </si>
-  <si>
-    <t>是否境外
-(0-否,1-是)
-(mpp时应该填写,不填默认0)</t>
-  </si>
-  <si>
-    <t>字段类型列表
-(json格式,不填的字段默认string类型)</t>
-  </si>
-  <si>
-    <t>数据载入模式
-(non-partitioned-append,
-non-partitioned-overwrite,
-partitioned-append,
-partitioned-overwrite)
-(hive4种,不填默认无分区追加)
-(mpp前两种,不填默认无分区追加)</t>
-  </si>
-  <si>
-    <t>分区信息
-(如:pt_dt='2022-01-01',age=18)
-(生成hive表且数据载入模式为有分区模式下应该填写,不填默认为:pt_dt=当日日期)</t>
-  </si>
-  <si>
-    <t>spark运行资源
-executor数量
-(不填默认4)</t>
-  </si>
-  <si>
-    <t>spark运行资源
-executor核数
-(不填默认4)</t>
-  </si>
-  <si>
-    <t>spark运行资源
-executor内存
-(不填默认8G)</t>
-  </si>
-  <si>
-    <t>spark运行资源
-driver数量
-(不填默认2)</t>
-  </si>
-  <si>
-    <t>spark运行资源
-driver内存
-(不填默认2G)</t>
-  </si>
-  <si>
-    <t>test1.xlsx</t>
-  </si>
-  <si>
-    <t>hive</t>
-  </si>
-  <si>
-    <t>bdsp_mpvs_t1</t>
-  </si>
-  <si>
-    <t>test1_hive</t>
-  </si>
-  <si>
-    <t>{"id":"int","name":"string","birthday":"date","salary":"double"}</t>
-  </si>
-  <si>
-    <t>partitioned-append</t>
-  </si>
-  <si>
-    <t>pt_dt='2022-01-01'</t>
-  </si>
-  <si>
-    <t>test2.xlsx</t>
-  </si>
-  <si>
-    <t>mpp</t>
-  </si>
-  <si>
-    <t>dwEGData0</t>
-  </si>
-  <si>
-    <t>test2_mpp</t>
-  </si>
-  <si>
-    <t>{"id":"int","birthday":"date","salary":"double"}</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="24"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -496,7 +379,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -617,172 +500,219 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -836,11 +766,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1129,171 +1122,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="7" width="20.6296296296296" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.6296296296296" style="1" customWidth="1"/>
-    <col min="9" max="9" width="28.8796296296296" style="1" customWidth="1"/>
-    <col min="10" max="14" width="20.6296296296296" style="1" customWidth="1"/>
+    <col width="20.6296296296296" customWidth="1" style="1" min="1" max="7"/>
+    <col width="31.6296296296296" customWidth="1" style="1" min="8" max="8"/>
+    <col width="28.8796296296296" customWidth="1" style="1" min="9" max="9"/>
+    <col width="20.6296296296296" customWidth="1" style="1" min="10" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.6" spans="1:14">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+    <row r="1" ht="30.6" customHeight="1" s="5">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>批量上传文件并生成数据表模板</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
+      <c r="J1" s="6" t="n"/>
+      <c r="K1" s="6" t="n"/>
+      <c r="L1" s="6" t="n"/>
+      <c r="M1" s="6" t="n"/>
+      <c r="N1" s="7" t="n"/>
     </row>
-    <row r="2" ht="100.8" spans="1:14">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>14</v>
+    <row r="2" ht="100.8" customHeight="1" s="5">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号
+(必填)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>文件名
+(必填,仅支持字母开头，且只能包含字母,下划线和数字;带后缀,支持txt,csv,xls,xlsx)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>目标表类型
+(必填,hive/mpp)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>目标库名
+(hive时必填可写库库名,mpp时必填mppSchema)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>目标表名
+(必填,bi_前缀不用填写,会自动拼接上)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>是否境外
+(0-否,1-是)
+(mpp时应该填写,不填默认0)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>字段类型列表
+(json格式,不填的字段默认string类型)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>数据载入模式
+(non-partitioned-append,
+non-partitioned-overwrite,
+partitioned-append,
+partitioned-overwrite)
+(hive4种,不填默认无分区追加)
+(mpp前两种,不填默认无分区追加)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>分区信息
+(如:pt_dt='2022-01-01',age=18)
+(生成hive表且数据载入模式为有分区模式下应该填写,不填默认为:pt_dt=当日日期)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>spark运行资源
+executor数量
+(不填默认4)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>spark运行资源
+executor核数
+(不填默认4)</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>spark运行资源
+executor内存
+(不填默认8G)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>spark运行资源
+driver数量
+(不填默认2)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>spark运行资源
+driver内存
+(不填默认2G)</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="57.6" spans="1:14">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-    </row>
-    <row r="4" ht="43.2" spans="1:14">
-      <c r="A4" s="4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-    </row>
+    <row r="3" ht="57.6" customHeight="1" s="5"/>
+    <row r="4" ht="43.2" customHeight="1" s="5"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>